--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
@@ -728,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="D2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="D3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="D4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
@@ -683,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,16 @@
           <t>calibration_quality</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_grade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -743,6 +753,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -769,6 +787,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -795,6 +821,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -821,6 +855,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -847,6 +889,14 @@
           <t>limited_regime_support</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -873,6 +923,14 @@
           <t>limited_regime_support</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -899,6 +957,14 @@
           <t>adequate</t>
         </is>
       </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -923,6 +989,14 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>supported</t>
         </is>
       </c>
     </row>
